--- a/andes/cases/npcc/npcc.xlsx
+++ b/andes/cases/npcc/npcc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hcui7/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\zzhuang7\repos\andes\andes\cases\npcc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A3AA0D-5F6C-B04A-813B-1931F04263E6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80C1DEE6-2EA8-4AF7-8B03-CDEFEE62D403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11460" yWindow="3580" windowWidth="21180" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3765" yWindow="3765" windowWidth="38700" windowHeight="15345" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Toggler" sheetId="11" r:id="rId1"/>
@@ -2013,9 +2013,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2053,9 +2053,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2088,26 +2088,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2140,26 +2123,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2334,9 +2300,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -2359,7 +2325,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2382,7 +2348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2413,9 +2379,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:N30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -2459,7 +2425,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -2500,7 +2466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -2541,7 +2507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -2582,7 +2548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -2623,7 +2589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -2664,7 +2630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -2705,7 +2671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -2746,7 +2712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -2787,7 +2753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -2828,7 +2794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -2869,7 +2835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -2910,7 +2876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -2951,7 +2917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -2992,7 +2958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -3033,7 +2999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -3074,7 +3040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -3115,7 +3081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -3156,7 +3122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -3197,7 +3163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -3238,7 +3204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -3279,7 +3245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -3320,7 +3286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -3361,7 +3327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -3402,7 +3368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -3443,7 +3409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -3484,7 +3450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -3525,7 +3491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -3566,7 +3532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -3607,7 +3573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -3656,9 +3622,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:T25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="33.28515625" customWidth="1"/>
+    <col min="4" max="4" width="46.140625" customWidth="1"/>
+    <col min="5" max="5" width="28.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -3720,7 +3691,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -3737,16 +3708,16 @@
         <v>524</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G2">
         <v>0.06</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>0.5</v>
@@ -3782,7 +3753,7 @@
         <v>1.73</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3799,16 +3770,16 @@
         <v>525</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G3">
         <v>0.02</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>0.79</v>
@@ -3844,7 +3815,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -3861,16 +3832,16 @@
         <v>526</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G4">
         <v>0.06</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>0.5</v>
@@ -3906,7 +3877,7 @@
         <v>1.73</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -3923,16 +3894,16 @@
         <v>527</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G5">
         <v>0.06</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>0.5</v>
@@ -3947,13 +3918,13 @@
         <v>50</v>
       </c>
       <c r="N5">
-        <v>-0.05</v>
+        <v>1</v>
       </c>
       <c r="O5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="Q5">
         <v>2</v>
@@ -3968,7 +3939,7 @@
         <v>1.73</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -3985,16 +3956,16 @@
         <v>528</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G6">
         <v>0.02</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>0.47</v>
@@ -4030,7 +4001,7 @@
         <v>1.73</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -4047,16 +4018,16 @@
         <v>529</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G7">
         <v>0.02</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <v>0.73</v>
@@ -4092,7 +4063,7 @@
         <v>1.5549999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -4109,16 +4080,16 @@
         <v>530</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G8">
         <v>0.02</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
         <v>1.4</v>
@@ -4154,7 +4125,7 @@
         <v>1.4650000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -4171,16 +4142,16 @@
         <v>531</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G9">
         <v>0.02</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>0.53</v>
@@ -4216,7 +4187,7 @@
         <v>1.4650000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -4233,16 +4204,16 @@
         <v>532</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G10">
         <v>0.05</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <v>0.40500000000000003</v>
@@ -4278,7 +4249,7 @@
         <v>1.73</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -4295,16 +4266,16 @@
         <v>533</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G11">
         <v>0.2</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
         <v>0.5</v>
@@ -4340,7 +4311,7 @@
         <v>2.0249999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -4357,16 +4328,16 @@
         <v>534</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G12">
         <v>0.2</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
         <v>0.27</v>
@@ -4402,7 +4373,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -4419,16 +4390,16 @@
         <v>535</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G13">
         <v>0.2</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
         <v>0.27</v>
@@ -4464,7 +4435,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -4481,16 +4452,16 @@
         <v>536</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G14">
         <v>0.06</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14">
         <v>0.5</v>
@@ -4526,7 +4497,7 @@
         <v>1.5249999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -4543,16 +4514,16 @@
         <v>537</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G15">
         <v>0.2</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
         <v>0.5</v>
@@ -4588,7 +4559,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -4605,16 +4576,16 @@
         <v>538</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G16">
         <v>0.05</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16">
         <v>0.4</v>
@@ -4650,7 +4621,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -4667,16 +4638,16 @@
         <v>539</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G17">
         <v>0.05</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17">
         <v>0.4</v>
@@ -4712,7 +4683,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -4729,16 +4700,16 @@
         <v>540</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G18">
         <v>0.2</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18">
         <v>0.5</v>
@@ -4774,7 +4745,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -4791,16 +4762,16 @@
         <v>541</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G19">
         <v>0.2</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19">
         <v>0.5</v>
@@ -4836,7 +4807,7 @@
         <v>1.667</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -4853,16 +4824,16 @@
         <v>542</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G20">
         <v>0.2</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20">
         <v>0.5</v>
@@ -4898,7 +4869,7 @@
         <v>2.06</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -4915,16 +4886,16 @@
         <v>543</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G21">
         <v>0.2</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21">
         <v>0.5</v>
@@ -4960,7 +4931,7 @@
         <v>1.667</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -4977,16 +4948,16 @@
         <v>544</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G22">
         <v>0.2</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22">
         <v>0.5</v>
@@ -5022,7 +4993,7 @@
         <v>2.0249999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -5039,16 +5010,16 @@
         <v>545</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G23">
         <v>0.06</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23">
         <v>0.5</v>
@@ -5084,7 +5055,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -5101,16 +5072,16 @@
         <v>546</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G24">
         <v>0.2</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24">
         <v>0.5</v>
@@ -5146,7 +5117,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -5163,16 +5134,16 @@
         <v>547</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G25">
         <v>0.06</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25">
         <v>0.5</v>
@@ -5216,9 +5187,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N141"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -5262,7 +5233,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -5306,7 +5277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -5350,7 +5321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -5394,7 +5365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -5438,7 +5409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -5482,7 +5453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -5526,7 +5497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -5570,7 +5541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -5614,7 +5585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -5658,7 +5629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -5702,7 +5673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -5746,7 +5717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -5790,7 +5761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -5834,7 +5805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -5878,7 +5849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -5922,7 +5893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -5966,7 +5937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -6010,7 +5981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -6054,7 +6025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -6098,7 +6069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -6142,7 +6113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -6186,7 +6157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -6230,7 +6201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -6274,7 +6245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -6318,7 +6289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -6362,7 +6333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -6406,7 +6377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -6450,7 +6421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -6494,7 +6465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -6538,7 +6509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -6582,7 +6553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -6626,7 +6597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -6670,7 +6641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -6714,7 +6685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -6758,7 +6729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -6802,7 +6773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -6846,7 +6817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -6890,7 +6861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -6934,7 +6905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -6978,7 +6949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -7022,7 +6993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -7066,7 +7037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -7110,7 +7081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -7154,7 +7125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -7198,7 +7169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -7242,7 +7213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -7286,7 +7257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -7330,7 +7301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -7374,7 +7345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -7418,7 +7389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -7462,7 +7433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -7506,7 +7477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -7550,7 +7521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -7594,7 +7565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -7638,7 +7609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -7682,7 +7653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -7726,7 +7697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -7770,7 +7741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -7814,7 +7785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -7858,7 +7829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -7902,7 +7873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -7946,7 +7917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -7990,7 +7961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -8034,7 +8005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -8078,7 +8049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -8122,7 +8093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -8166,7 +8137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -8210,7 +8181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -8254,7 +8225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -8298,7 +8269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -8342,7 +8313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -8386,7 +8357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -8430,7 +8401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -8474,7 +8445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -8518,7 +8489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -8562,7 +8533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -8606,7 +8577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -8650,7 +8621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -8694,7 +8665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -8738,7 +8709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -8782,7 +8753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -8826,7 +8797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -8870,7 +8841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -8914,7 +8885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -8958,7 +8929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -9002,7 +8973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -9046,7 +9017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -9090,7 +9061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -9134,7 +9105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>88</v>
       </c>
@@ -9178,7 +9149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>89</v>
       </c>
@@ -9222,7 +9193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>90</v>
       </c>
@@ -9266,7 +9237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>91</v>
       </c>
@@ -9310,7 +9281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>92</v>
       </c>
@@ -9354,7 +9325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>93</v>
       </c>
@@ -9398,7 +9369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>94</v>
       </c>
@@ -9442,7 +9413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>95</v>
       </c>
@@ -9486,7 +9457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>96</v>
       </c>
@@ -9530,7 +9501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>97</v>
       </c>
@@ -9574,7 +9545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>98</v>
       </c>
@@ -9618,7 +9589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>99</v>
       </c>
@@ -9662,7 +9633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>100</v>
       </c>
@@ -9706,7 +9677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>101</v>
       </c>
@@ -9750,7 +9721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>102</v>
       </c>
@@ -9794,7 +9765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>103</v>
       </c>
@@ -9838,7 +9809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>104</v>
       </c>
@@ -9882,7 +9853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>105</v>
       </c>
@@ -9926,7 +9897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>106</v>
       </c>
@@ -9970,7 +9941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>107</v>
       </c>
@@ -10014,7 +9985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>108</v>
       </c>
@@ -10058,7 +10029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>109</v>
       </c>
@@ -10102,7 +10073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>110</v>
       </c>
@@ -10146,7 +10117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>111</v>
       </c>
@@ -10190,7 +10161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>112</v>
       </c>
@@ -10234,7 +10205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>113</v>
       </c>
@@ -10278,7 +10249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>114</v>
       </c>
@@ -10322,7 +10293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>115</v>
       </c>
@@ -10366,7 +10337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>116</v>
       </c>
@@ -10410,7 +10381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>117</v>
       </c>
@@ -10454,7 +10425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>118</v>
       </c>
@@ -10498,7 +10469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>119</v>
       </c>
@@ -10542,7 +10513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>120</v>
       </c>
@@ -10586,7 +10557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>121</v>
       </c>
@@ -10630,7 +10601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>122</v>
       </c>
@@ -10674,7 +10645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>123</v>
       </c>
@@ -10718,7 +10689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>124</v>
       </c>
@@ -10762,7 +10733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>125</v>
       </c>
@@ -10806,7 +10777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>126</v>
       </c>
@@ -10850,7 +10821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>127</v>
       </c>
@@ -10894,7 +10865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>128</v>
       </c>
@@ -10938,7 +10909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>129</v>
       </c>
@@ -10982,7 +10953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>130</v>
       </c>
@@ -11026,7 +10997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>131</v>
       </c>
@@ -11070,7 +11041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>132</v>
       </c>
@@ -11114,7 +11085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>133</v>
       </c>
@@ -11158,7 +11129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>134</v>
       </c>
@@ -11202,7 +11173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>135</v>
       </c>
@@ -11246,7 +11217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>136</v>
       </c>
@@ -11290,7 +11261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>137</v>
       </c>
@@ -11334,7 +11305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>138</v>
       </c>
@@ -11378,7 +11349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>139</v>
       </c>
@@ -11430,9 +11401,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K93"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -11467,7 +11438,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -11502,7 +11473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -11537,7 +11508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -11572,7 +11543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -11607,7 +11578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -11642,7 +11613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -11677,7 +11648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -11712,7 +11683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -11747,7 +11718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -11782,7 +11753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -11817,7 +11788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -11852,7 +11823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -11887,7 +11858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -11922,7 +11893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -11957,7 +11928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -11992,7 +11963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -12027,7 +11998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -12062,7 +12033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -12097,7 +12068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -12132,7 +12103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -12167,7 +12138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -12202,7 +12173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -12237,7 +12208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -12272,7 +12243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -12307,7 +12278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -12342,7 +12313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -12377,7 +12348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -12412,7 +12383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -12447,7 +12418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -12482,7 +12453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -12517,7 +12488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -12552,7 +12523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -12587,7 +12558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -12622,7 +12593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -12657,7 +12628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -12692,7 +12663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -12727,7 +12698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -12762,7 +12733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -12797,7 +12768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -12832,7 +12803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -12867,7 +12838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -12902,7 +12873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -12937,7 +12908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -12972,7 +12943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -13007,7 +12978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -13042,7 +13013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -13077,7 +13048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -13112,7 +13083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -13147,7 +13118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -13182,7 +13153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -13217,7 +13188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -13252,7 +13223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -13287,7 +13258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -13322,7 +13293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -13357,7 +13328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -13392,7 +13363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -13427,7 +13398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -13462,7 +13433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -13497,7 +13468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -13532,7 +13503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -13567,7 +13538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -13602,7 +13573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -13637,7 +13608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -13672,7 +13643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -13707,7 +13678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -13742,7 +13713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -13777,7 +13748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -13812,7 +13783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -13847,7 +13818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -13882,7 +13853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -13917,7 +13888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -13952,7 +13923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -13987,7 +13958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -14022,7 +13993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -14057,7 +14028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -14092,7 +14063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -14127,7 +14098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -14162,7 +14133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -14197,7 +14168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -14232,7 +14203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -14267,7 +14238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -14302,7 +14273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -14337,7 +14308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -14372,7 +14343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -14407,7 +14378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -14442,7 +14413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -14477,7 +14448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -14512,7 +14483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -14547,7 +14518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>88</v>
       </c>
@@ -14582,7 +14553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>89</v>
       </c>
@@ -14617,7 +14588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>90</v>
       </c>
@@ -14652,7 +14623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>91</v>
       </c>
@@ -14695,9 +14666,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S48"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -14756,7 +14727,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -14812,7 +14783,7 @@
         <v>0.2175</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -14868,7 +14839,7 @@
         <v>0.20649999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -14924,7 +14895,7 @@
         <v>9.9900000000000003E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -14980,7 +14951,7 @@
         <v>0.2235</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -15036,7 +15007,7 @@
         <v>0.23200000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -15092,7 +15063,7 @@
         <v>0.20930000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -15148,7 +15119,7 @@
         <v>0.28170000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -15204,7 +15175,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -15260,7 +15231,7 @@
         <v>0.29899999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -15316,7 +15287,7 @@
         <v>0.17799999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -15372,7 +15343,7 @@
         <v>0.35189999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -15428,7 +15399,7 @@
         <v>0.39100000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -15484,7 +15455,7 @@
         <v>0.29499999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -15540,7 +15511,7 @@
         <v>6.1949999999999998E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -15596,7 +15567,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -15652,7 +15623,7 @@
         <v>0.32500000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -15708,7 +15679,7 @@
         <v>0.32500000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -15764,7 +15735,7 @@
         <v>0.3624</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -15820,7 +15791,7 @@
         <v>0.25750000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -15876,7 +15847,7 @@
         <v>0.16239999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -15932,7 +15903,7 @@
         <v>0.23535</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -15988,7 +15959,7 @@
         <v>0.18940000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -16044,7 +16015,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -16100,7 +16071,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -16156,7 +16127,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -16212,7 +16183,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -16268,7 +16239,7 @@
         <v>0.32200000000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -16324,7 +16295,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -16380,7 +16351,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -16436,7 +16407,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -16492,7 +16463,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -16548,7 +16519,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -16604,7 +16575,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -16660,7 +16631,7 @@
         <v>9.7500000000000003E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -16716,7 +16687,7 @@
         <v>0.22950000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -16772,7 +16743,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -16828,7 +16799,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -16884,7 +16855,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -16940,7 +16911,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -16996,7 +16967,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -17052,7 +17023,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -17108,7 +17079,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -17164,7 +17135,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -17220,7 +17191,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -17276,7 +17247,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -17332,7 +17303,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -17396,9 +17367,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:T2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -17460,7 +17431,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -17527,9 +17498,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:X234"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -17603,7 +17574,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -17668,7 +17639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -17733,7 +17704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -17798,7 +17769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -17863,7 +17834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -17928,7 +17899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -17993,7 +17964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -18058,7 +18029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -18123,7 +18094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -18188,7 +18159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -18253,7 +18224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -18318,7 +18289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -18383,7 +18354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -18448,7 +18419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -18513,7 +18484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -18578,7 +18549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -18643,7 +18614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -18708,7 +18679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -18773,7 +18744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -18838,7 +18809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -18903,7 +18874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -18968,7 +18939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -19033,7 +19004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -19098,7 +19069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -19163,7 +19134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -19228,7 +19199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -19293,7 +19264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -19358,7 +19329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -19423,7 +19394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -19488,7 +19459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -19553,7 +19524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -19618,7 +19589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -19683,7 +19654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -19748,7 +19719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -19813,7 +19784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -19878,7 +19849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -19943,7 +19914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -20008,7 +19979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -20073,7 +20044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -20138,7 +20109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -20203,7 +20174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -20268,7 +20239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -20333,7 +20304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -20398,7 +20369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -20463,7 +20434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -20528,7 +20499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -20593,7 +20564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -20658,7 +20629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -20723,7 +20694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -20788,7 +20759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -20853,7 +20824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -20918,7 +20889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -20983,7 +20954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -21048,7 +21019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -21113,7 +21084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -21178,7 +21149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -21243,7 +21214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -21308,7 +21279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -21373,7 +21344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -21438,7 +21409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -21503,7 +21474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -21568,7 +21539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -21633,7 +21604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -21698,7 +21669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -21763,7 +21734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -21828,7 +21799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -21893,7 +21864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -21958,7 +21929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -22023,7 +21994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -22088,7 +22059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -22153,7 +22124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -22218,7 +22189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -22283,7 +22254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -22348,7 +22319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -22413,7 +22384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -22478,7 +22449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -22543,7 +22514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -22608,7 +22579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -22673,7 +22644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -22738,7 +22709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -22803,7 +22774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -22868,7 +22839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -22933,7 +22904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -22998,7 +22969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -23063,7 +23034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -23128,7 +23099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -23193,7 +23164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -23258,7 +23229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -23323,7 +23294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>88</v>
       </c>
@@ -23388,7 +23359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>89</v>
       </c>
@@ -23453,7 +23424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>90</v>
       </c>
@@ -23518,7 +23489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>91</v>
       </c>
@@ -23583,7 +23554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>92</v>
       </c>
@@ -23648,7 +23619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>93</v>
       </c>
@@ -23713,7 +23684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>94</v>
       </c>
@@ -23778,7 +23749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>95</v>
       </c>
@@ -23843,7 +23814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>96</v>
       </c>
@@ -23908,7 +23879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>97</v>
       </c>
@@ -23973,7 +23944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>98</v>
       </c>
@@ -24038,7 +24009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>99</v>
       </c>
@@ -24103,7 +24074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>100</v>
       </c>
@@ -24168,7 +24139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>101</v>
       </c>
@@ -24233,7 +24204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>102</v>
       </c>
@@ -24298,7 +24269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>103</v>
       </c>
@@ -24363,7 +24334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>104</v>
       </c>
@@ -24428,7 +24399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>105</v>
       </c>
@@ -24493,7 +24464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>106</v>
       </c>
@@ -24558,7 +24529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>107</v>
       </c>
@@ -24623,7 +24594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>108</v>
       </c>
@@ -24688,7 +24659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>109</v>
       </c>
@@ -24753,7 +24724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>110</v>
       </c>
@@ -24818,7 +24789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>111</v>
       </c>
@@ -24883,7 +24854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>112</v>
       </c>
@@ -24948,7 +24919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>113</v>
       </c>
@@ -25013,7 +24984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>114</v>
       </c>
@@ -25078,7 +25049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>115</v>
       </c>
@@ -25143,7 +25114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>116</v>
       </c>
@@ -25208,7 +25179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>117</v>
       </c>
@@ -25273,7 +25244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>118</v>
       </c>
@@ -25338,7 +25309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>119</v>
       </c>
@@ -25403,7 +25374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>120</v>
       </c>
@@ -25468,7 +25439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>121</v>
       </c>
@@ -25533,7 +25504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>122</v>
       </c>
@@ -25598,7 +25569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>123</v>
       </c>
@@ -25663,7 +25634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>124</v>
       </c>
@@ -25728,7 +25699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>125</v>
       </c>
@@ -25793,7 +25764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>126</v>
       </c>
@@ -25858,7 +25829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>127</v>
       </c>
@@ -25923,7 +25894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>128</v>
       </c>
@@ -25988,7 +25959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>129</v>
       </c>
@@ -26053,7 +26024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>130</v>
       </c>
@@ -26118,7 +26089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>131</v>
       </c>
@@ -26183,7 +26154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>132</v>
       </c>
@@ -26248,7 +26219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>133</v>
       </c>
@@ -26313,7 +26284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>134</v>
       </c>
@@ -26378,7 +26349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>135</v>
       </c>
@@ -26443,7 +26414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>136</v>
       </c>
@@ -26508,7 +26479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>137</v>
       </c>
@@ -26573,7 +26544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>138</v>
       </c>
@@ -26638,7 +26609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>139</v>
       </c>
@@ -26703,7 +26674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>140</v>
       </c>
@@ -26768,7 +26739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>141</v>
       </c>
@@ -26833,7 +26804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>142</v>
       </c>
@@ -26898,7 +26869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>143</v>
       </c>
@@ -26963,7 +26934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>144</v>
       </c>
@@ -27028,7 +26999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>145</v>
       </c>
@@ -27093,7 +27064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>146</v>
       </c>
@@ -27158,7 +27129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>147</v>
       </c>
@@ -27223,7 +27194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>148</v>
       </c>
@@ -27288,7 +27259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>149</v>
       </c>
@@ -27353,7 +27324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>150</v>
       </c>
@@ -27418,7 +27389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>151</v>
       </c>
@@ -27483,7 +27454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>152</v>
       </c>
@@ -27548,7 +27519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>153</v>
       </c>
@@ -27613,7 +27584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>154</v>
       </c>
@@ -27678,7 +27649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>155</v>
       </c>
@@ -27743,7 +27714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>156</v>
       </c>
@@ -27808,7 +27779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>157</v>
       </c>
@@ -27873,7 +27844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>158</v>
       </c>
@@ -27938,7 +27909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>159</v>
       </c>
@@ -28003,7 +27974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>160</v>
       </c>
@@ -28068,7 +28039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>161</v>
       </c>
@@ -28133,7 +28104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>162</v>
       </c>
@@ -28198,7 +28169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>163</v>
       </c>
@@ -28263,7 +28234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>164</v>
       </c>
@@ -28328,7 +28299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>165</v>
       </c>
@@ -28393,7 +28364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>166</v>
       </c>
@@ -28458,7 +28429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>167</v>
       </c>
@@ -28523,7 +28494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>168</v>
       </c>
@@ -28588,7 +28559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>169</v>
       </c>
@@ -28653,7 +28624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>170</v>
       </c>
@@ -28718,7 +28689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>171</v>
       </c>
@@ -28783,7 +28754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>172</v>
       </c>
@@ -28848,7 +28819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>173</v>
       </c>
@@ -28913,7 +28884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>174</v>
       </c>
@@ -28978,7 +28949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>175</v>
       </c>
@@ -29043,7 +29014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>176</v>
       </c>
@@ -29108,7 +29079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>177</v>
       </c>
@@ -29173,7 +29144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>178</v>
       </c>
@@ -29238,7 +29209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>179</v>
       </c>
@@ -29303,7 +29274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>180</v>
       </c>
@@ -29368,7 +29339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>181</v>
       </c>
@@ -29433,7 +29404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>182</v>
       </c>
@@ -29498,7 +29469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>183</v>
       </c>
@@ -29563,7 +29534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>184</v>
       </c>
@@ -29628,7 +29599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>185</v>
       </c>
@@ -29693,7 +29664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>186</v>
       </c>
@@ -29758,7 +29729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>187</v>
       </c>
@@ -29823,7 +29794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>188</v>
       </c>
@@ -29888,7 +29859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>189</v>
       </c>
@@ -29953,7 +29924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>190</v>
       </c>
@@ -30018,7 +29989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>191</v>
       </c>
@@ -30083,7 +30054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>192</v>
       </c>
@@ -30148,7 +30119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>193</v>
       </c>
@@ -30213,7 +30184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>194</v>
       </c>
@@ -30278,7 +30249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>195</v>
       </c>
@@ -30343,7 +30314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>196</v>
       </c>
@@ -30408,7 +30379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>197</v>
       </c>
@@ -30473,7 +30444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>198</v>
       </c>
@@ -30538,7 +30509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>199</v>
       </c>
@@ -30603,7 +30574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <v>200</v>
       </c>
@@ -30668,7 +30639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>201</v>
       </c>
@@ -30733,7 +30704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>202</v>
       </c>
@@ -30798,7 +30769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>203</v>
       </c>
@@ -30863,7 +30834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>204</v>
       </c>
@@ -30928,7 +30899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>205</v>
       </c>
@@ -30993,7 +30964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>206</v>
       </c>
@@ -31058,7 +31029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <v>207</v>
       </c>
@@ -31123,7 +31094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>208</v>
       </c>
@@ -31188,7 +31159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <v>209</v>
       </c>
@@ -31253,7 +31224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <v>210</v>
       </c>
@@ -31318,7 +31289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <v>211</v>
       </c>
@@ -31383,7 +31354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <v>212</v>
       </c>
@@ -31448,7 +31419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <v>213</v>
       </c>
@@ -31513,7 +31484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <v>214</v>
       </c>
@@ -31578,7 +31549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <v>215</v>
       </c>
@@ -31643,7 +31614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <v>216</v>
       </c>
@@ -31708,7 +31679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <v>217</v>
       </c>
@@ -31773,7 +31744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <v>218</v>
       </c>
@@ -31838,7 +31809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <v>219</v>
       </c>
@@ -31903,7 +31874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <v>220</v>
       </c>
@@ -31968,7 +31939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <v>221</v>
       </c>
@@ -32033,7 +32004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <v>222</v>
       </c>
@@ -32098,7 +32069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <v>223</v>
       </c>
@@ -32163,7 +32134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
         <v>224</v>
       </c>
@@ -32228,7 +32199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
         <v>225</v>
       </c>
@@ -32293,7 +32264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <v>226</v>
       </c>
@@ -32358,7 +32329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
         <v>227</v>
       </c>
@@ -32423,7 +32394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
         <v>228</v>
       </c>
@@ -32488,7 +32459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
         <v>229</v>
       </c>
@@ -32553,7 +32524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
         <v>230</v>
       </c>
@@ -32618,7 +32589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
         <v>231</v>
       </c>
@@ -32683,7 +32654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
         <v>232</v>
       </c>
@@ -32756,9 +32727,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -32772,7 +32743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -32786,7 +32757,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -32800,7 +32771,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -32814,7 +32785,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -32828,7 +32799,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -32842,7 +32813,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -32864,9 +32835,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:S22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="35.28515625" customWidth="1"/>
+    <col min="4" max="4" width="47" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -32925,7 +32900,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -32981,7 +32956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -33037,7 +33012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -33093,7 +33068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -33149,7 +33124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -33205,7 +33180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -33261,7 +33236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -33317,7 +33292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -33373,7 +33348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -33429,7 +33404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -33485,7 +33460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -33541,7 +33516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -33597,7 +33572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -33653,7 +33628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -33709,7 +33684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -33765,7 +33740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -33821,7 +33796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -33877,7 +33852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -33933,7 +33908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -33989,7 +33964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -34045,7 +34020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -34109,9 +34084,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:AB28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="42.140625" customWidth="1"/>
+    <col min="4" max="4" width="45.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -34197,7 +34176,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -34280,7 +34259,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -34363,7 +34342,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -34446,7 +34425,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -34529,7 +34508,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -34612,7 +34591,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -34695,7 +34674,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -34778,7 +34757,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -34861,7 +34840,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -34944,7 +34923,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -35027,7 +35006,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -35110,7 +35089,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -35193,7 +35172,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -35276,7 +35255,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -35359,7 +35338,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -35442,7 +35421,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -35525,7 +35504,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -35608,7 +35587,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -35691,7 +35670,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -35774,7 +35753,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -35857,7 +35836,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -35940,7 +35919,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -36023,7 +36002,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -36106,7 +36085,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -36189,7 +36168,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -36272,7 +36251,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -36355,7 +36334,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>26</v>
       </c>
